--- a/workspace/framework_paper/edf-local/gradient_edf_local_eval_times.xlsx
+++ b/workspace/framework_paper/edf-local/gradient_edf_local_eval_times.xlsx
@@ -438,13 +438,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0533398436952848</v>
+        <v>0.002660519145429135</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1549574073031545</v>
+        <v>0.007923571555875242</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1030849986430258</v>
+        <v>0.1103513243980706</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06387289700331167</v>
+        <v>0.003137257522903383</v>
       </c>
       <c r="C3" t="n">
-        <v>0.183374385535717</v>
+        <v>0.009342472543939948</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1211944626597688</v>
+        <v>0.1687214089371264</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.07923487284919246</v>
+        <v>0.003370400760322809</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2339203097298741</v>
+        <v>0.01130968678742647</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3247490355931222</v>
+        <v>0.3615754944738001</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0906321017513983</v>
+        <v>0.003626262450125069</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3085540026240051</v>
+        <v>0.01142157420516014</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2938805027958006</v>
+        <v>0.3738928043935448</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1117391406325623</v>
+        <v>0.004139872535597533</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5193545945733785</v>
+        <v>0.01313319261185825</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7996679857373238</v>
+        <v>0.4306562354601919</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2203581779100932</v>
+        <v>0.004960935898125172</v>
       </c>
       <c r="C7" t="n">
-        <v>1.264149736147374</v>
+        <v>0.01461262839846313</v>
       </c>
       <c r="D7" t="n">
-        <v>2.903787835519761</v>
+        <v>0.7028398005478084</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1666425358783454</v>
+        <v>0.005957357496954501</v>
       </c>
       <c r="C8" t="n">
-        <v>2.562199874389917</v>
+        <v>0.03989080339670181</v>
       </c>
       <c r="D8" t="n">
-        <v>6.678555073766038</v>
+        <v>1.036453388538212</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.008202256737276911</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.04763089284300804</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1.233507547974587</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.006965220004785806</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.04663369895890355</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1.83080087646842</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.01135011486709118</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.07495825163088739</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3.625823009014129</v>
       </c>
     </row>
     <row r="12">

--- a/workspace/framework_paper/edf-local/gradient_edf_local_eval_times.xlsx
+++ b/workspace/framework_paper/edf-local/gradient_edf_local_eval_times.xlsx
@@ -438,13 +438,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.002660519145429135</v>
+        <v>0.004436774186324328</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007923571555875242</v>
+        <v>0.007494919961318374</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1103513243980706</v>
+        <v>0.1123024249542505</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.003137257522903383</v>
+        <v>0.005040931794792414</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009342472543939948</v>
+        <v>0.009365566540509462</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1687214089371264</v>
+        <v>0.1882425112742931</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.003370400760322809</v>
+        <v>0.005553760016337037</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01130968678742647</v>
+        <v>0.009382054256275297</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3615754944738001</v>
+        <v>0.3685008926782757</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003626262450125069</v>
+        <v>0.006277354233898223</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01142157420516014</v>
+        <v>0.01005127086304128</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3738928043935448</v>
+        <v>0.4050340062286705</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.004139872535597533</v>
+        <v>0.006877496675588191</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01313319261185825</v>
+        <v>0.0121993315871805</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4306562354601919</v>
+        <v>0.4844221117533744</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.004960935898125172</v>
+        <v>0.00696799824014306</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01461262839846313</v>
+        <v>0.01518268994055688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7028398005478084</v>
+        <v>0.8003150757774711</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.005957357496954501</v>
+        <v>0.008573888386599719</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03989080339670181</v>
+        <v>0.04547359433025121</v>
       </c>
       <c r="D8" t="n">
-        <v>1.036453388538212</v>
+        <v>1.232616999577731</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.008202256737276911</v>
+        <v>0.01098268416244537</v>
       </c>
       <c r="C9" t="n">
-        <v>0.04763089284300804</v>
+        <v>0.05649353932589293</v>
       </c>
       <c r="D9" t="n">
-        <v>1.233507547974587</v>
+        <v>1.50113120963797</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.006965220004785806</v>
+        <v>0.00886443154886365</v>
       </c>
       <c r="C10" t="n">
-        <v>0.04663369895890355</v>
+        <v>0.05557813871651888</v>
       </c>
       <c r="D10" t="n">
-        <v>1.83080087646842</v>
+        <v>2.215939767956734</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01135011486709118</v>
+        <v>0.01395250188419595</v>
       </c>
       <c r="C11" t="n">
-        <v>0.07495825163088739</v>
+        <v>0.08848234249278902</v>
       </c>
       <c r="D11" t="n">
-        <v>3.625823009014129</v>
+        <v>4.224970652461052</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.009710192447528243</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.412966146459803</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>25.21890632629395</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.01386420088121667</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.6617586286831647</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>7.774098954200745</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.01460287408204749</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.7520390724949538</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>9.2970436835289</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.03341091322479769</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.574850985594094</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>22.31281812667847</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.01497641820111312</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7.320290086232125</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>31.45615011692047</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.01528104004450142</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>6.355246095694602</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>60.48866271495819</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.0179513033630792</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>9.044642110019922</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>98.35680090427398</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>0.01757206165697426</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>14.58308600641787</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>147.1220757770538</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.01875561323016882</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>28.5107893371582</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>268.1389185333252</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>0.01843973661307246</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>70.0985567739606</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>429.6673047065735</v>
       </c>
     </row>
   </sheetData>
